--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="33">
   <si>
     <t xml:space="preserve">TestCase</t>
   </si>
@@ -107,6 +107,18 @@
   </si>
   <si>
     <t>Automation Public Portfolio_20260910_180946_775</t>
+  </si>
+  <si>
+    <t>Automation Portfolio_20260916_124321_613</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20260916_141749_507</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20260916_142052_057</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20260916_144038_045</t>
   </si>
 </sst>
 </file>
@@ -452,7 +464,7 @@
         <v>13</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" t="b" s="0">
         <v>0</v>
@@ -495,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="s" s="0">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C3" t="b" s="0">
         <v>1</v>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="180">
   <si>
     <t xml:space="preserve">TestCase</t>
   </si>
@@ -473,6 +473,93 @@
   </si>
   <si>
     <t>validateMyProductPortfolios</t>
+  </si>
+  <si>
+    <t>AddTeamsAndMembersToProduct</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260924_182820_023</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260924_182820_023: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260924_183147_837</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260924_183147_837: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260925_102912_743</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260925_102912_743: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260925_103413_199</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260925_103413_199: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260925_120815_652</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20260925_120815_652: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>AddProductToRelease</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20260928_081923_317</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20260928_081923_317: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Digital_20260928_081901_818</t>
+  </si>
+  <si>
+    <t>Digital Platform Hotfix_20260928_081912_145</t>
+  </si>
+  <si>
+    <t>ValidationOfCustomFields</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20260928_152816_158</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20260928_152816_158: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Custom Fields Product_20260928_164703_453</t>
+  </si>
+  <si>
+    <t>Automation Public Custom Fields Product_20260928_164703_453: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Custom Fields Product_20260928_165734_283</t>
+  </si>
+  <si>
+    <t>Automation Public Custom Fields Product_20260928_165734_283: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>downloadAuditHistoryInPdfAndCsvFormats</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20260928_170613_206</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20260928_170948_480</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20260928_172347_502</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20260928_172732_811</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20260928_172939_485</t>
   </si>
 </sst>
 </file>
@@ -762,7 +849,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" hidden="false" style="0" width="27.15" collapsed="false" outlineLevel="0"/>
@@ -1715,6 +1802,170 @@
         <v>21</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M24" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L25" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="M25" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="C27" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M27" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="184">
   <si>
     <t xml:space="preserve">TestCase</t>
   </si>
@@ -560,6 +560,18 @@
   </si>
   <si>
     <t>Automation Report Portfolio_20260928_172939_485</t>
+  </si>
+  <si>
+    <t>EditPortfolioDetailsOfExistingProduct</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20260929_132500_259</t>
+  </si>
+  <si>
+    <t>Automation Product_20260929_132436_044</t>
+  </si>
+  <si>
+    <t>Automation Product_20260929_132436_044: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -849,7 +861,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" hidden="false" style="0" width="27.15" collapsed="false" outlineLevel="0"/>
@@ -1966,6 +1978,47 @@
         <v>21</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="C28" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M28" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="193">
   <si>
     <t xml:space="preserve">TestCase</t>
   </si>
@@ -572,6 +572,33 @@
   </si>
   <si>
     <t>Automation Product_20260929_132436_044: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20260929_135503_976</t>
+  </si>
+  <si>
+    <t>Automation Product_20260929_135439_778</t>
+  </si>
+  <si>
+    <t>Automation Product_20260929_135439_778: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20260929_135939_935</t>
+  </si>
+  <si>
+    <t>Automation Product_20260929_135910_097</t>
+  </si>
+  <si>
+    <t>Automation Product_20260929_135910_097: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20260929_140454_551</t>
+  </si>
+  <si>
+    <t>Automation Product_20260929_140429_742</t>
+  </si>
+  <si>
+    <t>Automation Product_20260929_140429_742: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -1983,16 +2010,16 @@
         <v>180</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C28" t="b" s="0">
         <v>0</v>
       </c>
       <c r="D28" t="s" s="0">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="E28" t="s" s="0">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F28" t="s" s="0">
         <v>21</v>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29" count="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40" count="147">
   <si>
     <t>TestCase</t>
   </si>
@@ -98,6 +98,39 @@
   </si>
   <si>
     <t>Automation Public Product_20261001_145127_387: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>downloadAuditHistoryInPdfAndCsvFormats</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20261012_124704_626</t>
+  </si>
+  <si>
+    <t>createPublicPortfolioWithAllFields</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20261012_140551_098</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20261012_141035_568</t>
+  </si>
+  <si>
+    <t>addMultipleYearFinancials</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20261012_142003_623</t>
+  </si>
+  <si>
+    <t>editExistingPortfolio</t>
+  </si>
+  <si>
+    <t>Automation Portfolio Edited_20261012_142146_808</t>
+  </si>
+  <si>
+    <t>editWorkflowTemplate</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20261012_142239_370</t>
   </si>
 </sst>
 </file>
@@ -1254,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -1473,6 +1506,211 @@
         <v>15</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="C6" t="b" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M6" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="C7" t="b" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K7" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M7" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="1">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="C8" t="b" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I8" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K8" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M8" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="C9" t="b" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M9" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="1">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s" s="1">
+        <v>39</v>
+      </c>
+      <c r="C10" t="b" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K10" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M10" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811" footer="0.511811"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40" count="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47" count="183">
   <si>
     <t>TestCase</t>
   </si>
@@ -131,6 +131,27 @@
   </si>
   <si>
     <t>Automation Public Portfolio_20261012_142239_370</t>
+  </si>
+  <si>
+    <t>portfolio_1747</t>
+  </si>
+  <si>
+    <t>Automation Product_20261013_165649_825</t>
+  </si>
+  <si>
+    <t>Automation Product_20261013_165649_825: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>createPrivatePortfolioWithMandatoryFields</t>
+  </si>
+  <si>
+    <t>Automation Portfolio_20261013_165808_736</t>
+  </si>
+  <si>
+    <t>Automation Product_20261013_173637_565</t>
+  </si>
+  <si>
+    <t>Automation Product_20261013_173637_565: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -1429,16 +1450,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F4" t="s" s="1">
         <v>15</v>
@@ -1708,6 +1729,47 @@
         <v>15</v>
       </c>
       <c r="M10" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="C11" t="b" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I11" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K11" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M11" t="s" s="1">
         <v>15</v>
       </c>
     </row>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47" count="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="102" count="422">
   <si>
     <t>TestCase</t>
   </si>
@@ -152,6 +152,171 @@
   </si>
   <si>
     <t>Automation Product_20261013_173637_565: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>AddProductToRelease</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_115924_804</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_115924_804: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Digital_20261014_115905_202</t>
+  </si>
+  <si>
+    <t>Digital Platform Hotfix_20261014_115913_556</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_132230_150</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_132230_150: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Digital_20261014_132204_857</t>
+  </si>
+  <si>
+    <t>Digital Platform Hotfix_20261014_132215_899</t>
+  </si>
+  <si>
+    <t>EditPortfolioDetailsOfExistingProduct</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20261014_132619_873</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_132557_685</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_132557_685: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>EditProductwithAddAndRemoveRelease</t>
+  </si>
+  <si>
+    <t>Automation Private Release Membership Product_20261014_132902_872</t>
+  </si>
+  <si>
+    <t>Automation Private Release Membership Product_20261014_132902_872: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>ValidationOfCustomFields</t>
+  </si>
+  <si>
+    <t>Automation Public Custom Fields Product_20261014_135228_288</t>
+  </si>
+  <si>
+    <t>Automation Public Custom Fields Product_20261014_135228_288: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_135400_153</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_135400_153: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261014_135516_245</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261014_135516_245: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>createPrivateProductWithDefineAndDesignPhase</t>
+  </si>
+  <si>
+    <t>Automation Private Define Design Product_20261014_135641_763</t>
+  </si>
+  <si>
+    <t>Automation Private Define Design Product_20261014_135641_763: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>createPrivateProductWithDefinePhase</t>
+  </si>
+  <si>
+    <t>Automation Private Define Product_20261014_135821_076</t>
+  </si>
+  <si>
+    <t>Automation Private Define Product_20261014_135821_076: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>createPrivateProductWithDesignPhase</t>
+  </si>
+  <si>
+    <t>Automation Private Design Product_20261014_135941_429</t>
+  </si>
+  <si>
+    <t>Automation Private Design Product_20261014_135941_429: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_140118_924</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_140118_924: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>createPublicProductWithAllFields</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261014_140235_495</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261014_140235_495: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_140118_924: Automation Linked Feature For Deletion_20261014_140359_610</t>
+  </si>
+  <si>
+    <t>Automation Linked Feature For Deletion_20261014_140359_610: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>CreatePrivateProductAndAddDependencyBetweenProducts</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261014_140621_567, Automation Private Dependency Product_20261014_140642_494</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261014_140621_567: Define, Design, Develop, Deploy, Automation Private Dependency Product_20261014_140642_494: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>createPrivateProductWithDevelopAndDesignPhase</t>
+  </si>
+  <si>
+    <t>Automation Private Develop Design Product_20261014_140932_703</t>
+  </si>
+  <si>
+    <t>Automation Private Develop Design Product_20261014_140932_703: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_151153_891</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_151153_891: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Digital_20261014_151120_437</t>
+  </si>
+  <si>
+    <t>Digital Platform Hotfix_20261014_151136_620</t>
+  </si>
+  <si>
+    <t>EditProductWithUpdatingPhases</t>
+  </si>
+  <si>
+    <t>Automation Private Phase Update Product_20261014_152526_489</t>
+  </si>
+  <si>
+    <t>Automation Private Phase Update Product_20261014_152526_489: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>SaveProductWithoutMandatoryFieldsAndVerifyErrorMessages</t>
+  </si>
+  <si>
+    <t>Automation Mandatory Validation Product_20261014_154007_848</t>
+  </si>
+  <si>
+    <t>Automation Mandatory Validation Product_20261014_154007_848: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -1374,10 +1539,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="s" s="1">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s" s="1">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s" s="1">
         <v>15</v>
@@ -1415,10 +1580,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="s" s="1">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s" s="1">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s" s="1">
         <v>15</v>
@@ -1450,16 +1615,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="F4" t="s" s="1">
         <v>15</v>
@@ -1497,16 +1662,16 @@
         <v>15</v>
       </c>
       <c r="D5" t="s" s="1">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s" s="1">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="F5" t="s" s="1">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s" s="1">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="1">
         <v>15</v>
@@ -1770,6 +1935,498 @@
         <v>15</v>
       </c>
       <c r="M11" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="E12" t="s" s="1">
+        <v>93</v>
+      </c>
+      <c r="F12" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K12" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s" s="1">
+        <v>94</v>
+      </c>
+      <c r="M12" t="s" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="1">
+        <v>56</v>
+      </c>
+      <c r="B13" t="s" s="1">
+        <v>57</v>
+      </c>
+      <c r="C13" t="b" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s" s="1">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s" s="1">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K13" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M13" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="1">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s" s="1">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s" s="1">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L14" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M14" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="1">
+        <v>63</v>
+      </c>
+      <c r="B15" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I15" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K15" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L15" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M15" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="1">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="F16" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K16" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M16" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s" s="1">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s" s="1">
+        <v>75</v>
+      </c>
+      <c r="F17" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I17" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K17" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L17" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M17" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="1">
+        <v>76</v>
+      </c>
+      <c r="B18" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s" s="1">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s" s="1">
+        <v>78</v>
+      </c>
+      <c r="F18" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K18" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L18" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M18" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="1">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s" s="1">
+        <v>82</v>
+      </c>
+      <c r="E19" t="s" s="1">
+        <v>83</v>
+      </c>
+      <c r="F19" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L19" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M19" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s" s="1">
+        <v>87</v>
+      </c>
+      <c r="E20" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="F20" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I20" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K20" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L20" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M20" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="1">
+        <v>89</v>
+      </c>
+      <c r="B21" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s" s="1">
+        <v>90</v>
+      </c>
+      <c r="E21" t="s" s="1">
+        <v>91</v>
+      </c>
+      <c r="F21" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I21" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K21" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L21" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M21" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>96</v>
+      </c>
+      <c r="B22" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s" s="1">
+        <v>97</v>
+      </c>
+      <c r="E22" t="s" s="1">
+        <v>98</v>
+      </c>
+      <c r="F22" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I22" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J22" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K22" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M22" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>99</v>
+      </c>
+      <c r="B23" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s" s="1">
+        <v>100</v>
+      </c>
+      <c r="E23" t="s" s="1">
+        <v>101</v>
+      </c>
+      <c r="F23" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I23" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J23" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K23" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L23" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M23" t="s" s="1">
         <v>15</v>
       </c>
     </row>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="102" count="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="180" count="802">
   <si>
     <t>TestCase</t>
   </si>
@@ -317,6 +317,240 @@
   </si>
   <si>
     <t>Automation Mandatory Validation Product_20261014_154007_848: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_162753_783</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_162753_783: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Digital_20261014_162733_959</t>
+  </si>
+  <si>
+    <t>Digital Platform Hotfix_20261014_162746_065</t>
+  </si>
+  <si>
+    <t>AddTeamsAndMembersToProduct</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20261014_162943_277</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20261014_162943_277: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20261014_163230_377</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_163208_790</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_163208_790: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_171920_515</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_171920_515: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Define Design Product_20261014_172224_994</t>
+  </si>
+  <si>
+    <t>Automation Private Define Design Product_20261014_172224_994: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Define Product_20261014_172404_674</t>
+  </si>
+  <si>
+    <t>Automation Private Define Product_20261014_172404_674: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Design Product_20261014_172613_877</t>
+  </si>
+  <si>
+    <t>Automation Private Design Product_20261014_172613_877: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_172807_287</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_172807_287: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261014_172807_287: Automation Linked Feature For Deletion_20261014_173054_408</t>
+  </si>
+  <si>
+    <t>Automation Linked Feature For Deletion_20261014_173054_408: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_184757_830</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261014_184757_830: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Digital_20261014_184739_799</t>
+  </si>
+  <si>
+    <t>Digital Platform Hotfix_20261014_184750_178</t>
+  </si>
+  <si>
+    <t>Automation Private Release Membership Product_20261014_185849_555</t>
+  </si>
+  <si>
+    <t>Automation Private Release Membership Product_20261014_185849_555: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261015_090901_515</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261015_090901_515: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Digital_20261015_090845_685</t>
+  </si>
+  <si>
+    <t>Digital Platform Hotfix_20261015_090854_225</t>
+  </si>
+  <si>
+    <t>Automation Private Release Membership Product_20261015_091043_487</t>
+  </si>
+  <si>
+    <t>Automation Private Release Membership Product_20261015_091043_487: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261015_091357_851</t>
+  </si>
+  <si>
+    <t>Automation Private Release Product_20261015_091357_851: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Digital_20261015_091337_947</t>
+  </si>
+  <si>
+    <t>Digital Platform Hotfix_20261015_091349_717</t>
+  </si>
+  <si>
+    <t>Automation Private Release Membership Product_20261015_091552_523</t>
+  </si>
+  <si>
+    <t>Automation Private Release Membership Product_20261015_091552_523: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261015_092614_736</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261015_092614_736: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Custom Fields Product_20261015_093027_037</t>
+  </si>
+  <si>
+    <t>Automation Public Custom Fields Product_20261015_093027_037: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20261015_093619_783</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_093556_342</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_093556_342: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20261015_094601_531</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_094532_561</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_094532_561: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20261015_094921_387</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_094843_686</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_094843_686: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20261015_095217_692</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_095149_439</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_095149_439: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Updated Existing Product Portfolio_20261015_095452_792</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_095433_481</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_095433_481: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>EditProductWithAlltheFields</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261015_101540_437</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261015_101540_437: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261015_104211_051</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261015_104211_051: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261015_104618_189</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261015_104618_189: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_105434_550</t>
+  </si>
+  <si>
+    <t>Automation Product_20261015_105434_550: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261015_105718_005</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261015_105718_005: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20261015_110104_187</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20261015_110104_187: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261015_110329_849</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261015_110329_849: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20261015_112551_238</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20261015_112551_238: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20261015_114028_047</t>
+  </si>
+  <si>
+    <t>Automation Private Team Allocation Product_20261015_114028_047: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -1473,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -1533,16 +1767,16 @@
         <v>13</v>
       </c>
       <c r="B2" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D2" t="s" s="1">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s" s="1">
-        <v>67</v>
+        <v>169</v>
       </c>
       <c r="F2" t="s" s="1">
         <v>15</v>
@@ -1574,16 +1808,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D3" t="s" s="1">
-        <v>68</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s" s="1">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="F3" t="s" s="1">
         <v>15</v>
@@ -1615,16 +1849,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="F4" t="s" s="1">
         <v>15</v>
@@ -1656,22 +1890,22 @@
         <v>24</v>
       </c>
       <c r="B5" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D5" t="s" s="1">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s" s="1">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="F5" t="s" s="1">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="G5" t="s" s="1">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="H5" t="s" s="1">
         <v>15</v>
@@ -1949,10 +2183,10 @@
         <v>15</v>
       </c>
       <c r="D12" t="s" s="1">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s" s="1">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="F12" t="s" s="1">
         <v>15</v>
@@ -1973,10 +2207,10 @@
         <v>15</v>
       </c>
       <c r="L12" t="s" s="1">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="M12" t="s" s="1">
-        <v>95</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1984,16 +2218,16 @@
         <v>56</v>
       </c>
       <c r="B13" t="s" s="1">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="C13" t="b" s="1">
         <v>0</v>
       </c>
       <c r="D13" t="s" s="1">
-        <v>58</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s" s="1">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="F13" t="s" s="1">
         <v>15</v>
@@ -2025,16 +2259,16 @@
         <v>60</v>
       </c>
       <c r="B14" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D14" t="s" s="1">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s" s="1">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="F14" t="s" s="1">
         <v>15</v>
@@ -2066,16 +2300,16 @@
         <v>63</v>
       </c>
       <c r="B15" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D15" t="s" s="1">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s" s="1">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="F15" t="s" s="1">
         <v>15</v>
@@ -2107,16 +2341,16 @@
         <v>70</v>
       </c>
       <c r="B16" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D16" t="s" s="1">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s" s="1">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s" s="1">
         <v>15</v>
@@ -2148,16 +2382,16 @@
         <v>73</v>
       </c>
       <c r="B17" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D17" t="s" s="1">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s" s="1">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="F17" t="s" s="1">
         <v>15</v>
@@ -2189,16 +2423,16 @@
         <v>76</v>
       </c>
       <c r="B18" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D18" t="s" s="1">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s" s="1">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="F18" t="s" s="1">
         <v>15</v>
@@ -2230,16 +2464,16 @@
         <v>81</v>
       </c>
       <c r="B19" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D19" t="s" s="1">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="E19" t="s" s="1">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="F19" t="s" s="1">
         <v>15</v>
@@ -2427,6 +2661,88 @@
         <v>15</v>
       </c>
       <c r="M23" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>106</v>
+      </c>
+      <c r="B24" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s" s="1">
+        <v>178</v>
+      </c>
+      <c r="E24" t="s" s="1">
+        <v>179</v>
+      </c>
+      <c r="F24" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I24" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J24" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L24" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M24" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="1">
+        <v>161</v>
+      </c>
+      <c r="B25" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s" s="1">
+        <v>166</v>
+      </c>
+      <c r="E25" t="s" s="1">
+        <v>167</v>
+      </c>
+      <c r="F25" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I25" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J25" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K25" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L25" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M25" t="s" s="1">
         <v>15</v>
       </c>
     </row>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="180" count="802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="211" count="1045">
   <si>
     <t>TestCase</t>
   </si>
@@ -551,6 +551,99 @@
   </si>
   <si>
     <t>Automation Private Team Allocation Product_20261015_114028_047: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Develop Design Product_20261015_115022_847</t>
+  </si>
+  <si>
+    <t>Automation Private Develop Design Product_20261015_115022_847: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_120052_477, Automation Private Dependency Product_20261015_120111_015</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_120052_477: Define, Design, Develop, Deploy, Automation Private Dependency Product_20261015_120111_015: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_120715_235, Automation Private Dependency Product_20261015_120745_026</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_120715_235: Define, Design, Develop, Deploy, Automation Private Dependency Product_20261015_120745_026: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_121029_881, Automation Private Dependency Product_20261015_121048_067</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_121029_881: Define, Design, Develop, Deploy, Automation Private Dependency Product_20261015_121048_067: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_121415_622, Automation Private Dependency Product_20261015_121441_196</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_121415_622: Define, Design, Develop, Deploy, Automation Private Dependency Product_20261015_121441_196: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_121720_489, Automation Private Dependency Product_20261015_121737_038</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_121720_489: Define, Design, Develop, Deploy, Automation Private Dependency Product_20261015_121737_038: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_122229_841, Automation Private Dependency Product_20261015_122250_267</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261015_122229_841: Define, Design, Develop, Deploy, Automation Private Dependency Product_20261015_122250_267: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Mandatory Validation Product_20261015_122537_184</t>
+  </si>
+  <si>
+    <t>Automation Mandatory Validation Product_20261015_122537_184: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Mandatory Validation Product_20261015_122814_604</t>
+  </si>
+  <si>
+    <t>Automation Mandatory Validation Product_20261015_122814_604: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20261015_124835_764</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20261015_125059_531</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20261015_131943_639</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20261015_132543_164</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20261015_133040_077</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20261015_133441_633</t>
+  </si>
+  <si>
+    <t>Automation Report Portfolio_20261015_133856_253</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20261015_134109_911</t>
+  </si>
+  <si>
+    <t>cancelPortfolioCreation</t>
+  </si>
+  <si>
+    <t>Automation Portfolio_20261015_134321_609</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20261015_134426_709</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261015_144937_631</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261015_144937_631: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -1707,7 +1800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -1931,7 +2024,7 @@
         <v>29</v>
       </c>
       <c r="B6" t="s" s="1">
-        <v>30</v>
+        <v>204</v>
       </c>
       <c r="C6" t="b" s="1">
         <v>0</v>
@@ -1972,7 +2065,7 @@
         <v>31</v>
       </c>
       <c r="B7" t="s" s="1">
-        <v>33</v>
+        <v>208</v>
       </c>
       <c r="C7" t="b" s="1">
         <v>1</v>
@@ -2013,7 +2106,7 @@
         <v>34</v>
       </c>
       <c r="B8" t="s" s="1">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="C8" t="b" s="1">
         <v>1</v>
@@ -2136,7 +2229,7 @@
         <v>43</v>
       </c>
       <c r="B11" t="s" s="1">
-        <v>44</v>
+        <v>207</v>
       </c>
       <c r="C11" t="b" s="1">
         <v>0</v>
@@ -2470,10 +2563,10 @@
         <v>15</v>
       </c>
       <c r="D19" t="s" s="1">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="E19" t="s" s="1">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="F19" t="s" s="1">
         <v>15</v>
@@ -2505,16 +2598,16 @@
         <v>86</v>
       </c>
       <c r="B20" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D20" t="s" s="1">
-        <v>87</v>
+        <v>192</v>
       </c>
       <c r="E20" t="s" s="1">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="F20" t="s" s="1">
         <v>15</v>
@@ -2546,16 +2639,16 @@
         <v>89</v>
       </c>
       <c r="B21" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D21" t="s" s="1">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="E21" t="s" s="1">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="F21" t="s" s="1">
         <v>15</v>
@@ -2634,10 +2727,10 @@
         <v>15</v>
       </c>
       <c r="D23" t="s" s="1">
-        <v>100</v>
+        <v>196</v>
       </c>
       <c r="E23" t="s" s="1">
-        <v>101</v>
+        <v>197</v>
       </c>
       <c r="F23" t="s" s="1">
         <v>15</v>
@@ -2743,6 +2836,47 @@
         <v>15</v>
       </c>
       <c r="M25" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="1">
+        <v>206</v>
+      </c>
+      <c r="B26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="F26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L26" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M26" t="s" s="1">
         <v>15</v>
       </c>
     </row>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -6,12 +6,13 @@
   </bookViews>
   <sheets>
     <sheet name="ProE2E" sheetId="1" r:id="rId4"/>
+    <sheet name="MaturityAssessments" r:id="rId5" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="211" count="1045">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="224" count="1063">
   <si>
     <t>TestCase</t>
   </si>
@@ -644,6 +645,45 @@
   </si>
   <si>
     <t>Automation Public Product_20261015_144937_631: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>AssessmentName</t>
+  </si>
+  <si>
+    <t>MaturityAssesmentAtOrganisationLevel</t>
+  </si>
+  <si>
+    <t>Organization Automation and AI Readiness_20261020_195258_768</t>
+  </si>
+  <si>
+    <t>Organization Automation and AI Readiness_20261020_200619_684</t>
+  </si>
+  <si>
+    <t>MaturityAssesmentOrganisationRespondToAssesement</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_095352_404</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_101536_356</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_102226_124</t>
+  </si>
+  <si>
+    <t>IntiateAndDiscardMaturityAssessmentAtOrgLevel</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_151013_455</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_151149_527</t>
+  </si>
+  <si>
+    <t>BaseLineOrganisationMaturtiyAssesement</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_163036_437</t>
   </si>
 </sst>
 </file>
@@ -2887,4 +2927,54 @@
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="224" count="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="285" count="1380">
   <si>
     <t>TestCase</t>
   </si>
@@ -684,6 +684,189 @@
   </si>
   <si>
     <t>Org Maturity_20261021_163036_437</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_213303_187</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_213456_309</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_213843_353</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261021_214150_533</t>
+  </si>
+  <si>
+    <t>VerifyMaturityAssessmentInCurrentAssessment</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261021_215552_518</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261021_215552_518: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>VerifyMaturityAssessmentInBaselinedAssessment</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_100255_825</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_100255_825: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_101900_428</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_101900_428: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261022_121155_484</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261022_121155_484: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261022_121819_480</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261022_121819_480: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261022_123057_856</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261022_123057_856: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261022_130122_596</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261022_130122_596: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>VerifyTeamLevelMaturityAssessmentInBaselinedAssessment</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_131552_948</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_131552_948: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>VerifyTeamLevelMaturityAssessmentInCurrentAssessment</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_132221_731</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_132221_731: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_133114_962</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_133114_962: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_134751_289</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_134751_289: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_135410_504</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_135410_504: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Portfolio Edited_20261022_141444_841</t>
+  </si>
+  <si>
+    <t>Automation Portfolio Edited_20261022_141620_268</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20261022_144829_057</t>
+  </si>
+  <si>
+    <t>Automation Public Portfolio_20261022_145052_567</t>
+  </si>
+  <si>
+    <t>MaturityAssesmentTeamLevelwithSprint</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261022_154239_814</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261022_154239_814: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261022_155108_597</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261022_155108_597: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261022_155716_860</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261022_155716_860: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>MaturityAssessmentCompletedTeamLevelAssessmentValidation</t>
+  </si>
+  <si>
+    <t>AutomationPortfolio_20261022_162122_725</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_162134_002</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_162134_002: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>AutomationPortfolio_20261022_162600_997</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_162606_795</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261022_162606_795: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>SaveMaturityAssessmentWithoutSubmitting</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_163419_184</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_163419_184: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_165258_579</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_165258_579: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_165739_269</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_165739_269: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_170117_042</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_170117_042: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_170526_682</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261022_170526_682: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -1840,7 +2023,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -1947,10 +2130,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="s" s="1">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="E3" t="s" s="1">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="F3" t="s" s="1">
         <v>15</v>
@@ -2187,7 +2370,7 @@
         <v>36</v>
       </c>
       <c r="B9" t="s" s="1">
-        <v>37</v>
+        <v>257</v>
       </c>
       <c r="C9" t="b" s="1">
         <v>0</v>
@@ -2228,7 +2411,7 @@
         <v>38</v>
       </c>
       <c r="B10" t="s" s="1">
-        <v>39</v>
+        <v>259</v>
       </c>
       <c r="C10" t="b" s="1">
         <v>1</v>
@@ -2917,6 +3100,293 @@
         <v>15</v>
       </c>
       <c r="M26" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="1">
+        <v>228</v>
+      </c>
+      <c r="B27" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s" s="1">
+        <v>229</v>
+      </c>
+      <c r="E27" t="s" s="1">
+        <v>230</v>
+      </c>
+      <c r="F27" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I27" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J27" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K27" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L27" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M27" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1">
+        <v>231</v>
+      </c>
+      <c r="B28" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s" s="1">
+        <v>234</v>
+      </c>
+      <c r="E28" t="s" s="1">
+        <v>235</v>
+      </c>
+      <c r="F28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M28" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
+        <v>244</v>
+      </c>
+      <c r="B29" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s" s="1">
+        <v>254</v>
+      </c>
+      <c r="E29" t="s" s="1">
+        <v>255</v>
+      </c>
+      <c r="F29" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H29" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I29" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J29" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L29" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M29" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1">
+        <v>247</v>
+      </c>
+      <c r="B30" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s" s="1">
+        <v>252</v>
+      </c>
+      <c r="E30" t="s" s="1">
+        <v>253</v>
+      </c>
+      <c r="F30" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H30" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I30" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J30" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K30" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L30" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M30" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="1">
+        <v>260</v>
+      </c>
+      <c r="B31" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s" s="1">
+        <v>265</v>
+      </c>
+      <c r="E31" t="s" s="1">
+        <v>266</v>
+      </c>
+      <c r="F31" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J31" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K31" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L31" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M31" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="1">
+        <v>267</v>
+      </c>
+      <c r="B32" t="s" s="1">
+        <v>271</v>
+      </c>
+      <c r="C32" t="b" s="1">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s" s="1">
+        <v>272</v>
+      </c>
+      <c r="E32" t="s" s="1">
+        <v>273</v>
+      </c>
+      <c r="F32" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H32" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I32" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J32" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K32" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L32" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M32" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="1">
+        <v>274</v>
+      </c>
+      <c r="B33" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s" s="1">
+        <v>283</v>
+      </c>
+      <c r="E33" t="s" s="1">
+        <v>284</v>
+      </c>
+      <c r="F33" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H33" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I33" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J33" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K33" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L33" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M33" t="s" s="1">
         <v>15</v>
       </c>
     </row>
@@ -2947,7 +3417,7 @@
         <v>212</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>214</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3">
@@ -2955,7 +3425,7 @@
         <v>215</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4">
@@ -2963,7 +3433,7 @@
         <v>219</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
@@ -2971,7 +3441,7 @@
         <v>222</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="285" count="1380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="292" count="1415">
   <si>
     <t>TestCase</t>
   </si>
@@ -867,6 +867,27 @@
   </si>
   <si>
     <t>Automation Private Product Maturity Assessment_20261022_170526_682: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261022_190914_928</t>
+  </si>
+  <si>
+    <t>Automation Product_20261022_190914_928: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Portfolio_20261022_191540_233</t>
+  </si>
+  <si>
+    <t>deletePortfolioWithProduct</t>
+  </si>
+  <si>
+    <t>Automation Portfolio_20261022_191836_629</t>
+  </si>
+  <si>
+    <t>Automation Product_20261022_191858_071</t>
+  </si>
+  <si>
+    <t>Automation Product_20261022_191858_071: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -2023,7 +2044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -2171,10 +2192,10 @@
         <v>15</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>121</v>
+        <v>286</v>
       </c>
       <c r="F4" t="s" s="1">
         <v>15</v>
@@ -2452,7 +2473,7 @@
         <v>43</v>
       </c>
       <c r="B11" t="s" s="1">
-        <v>207</v>
+        <v>287</v>
       </c>
       <c r="C11" t="b" s="1">
         <v>0</v>
@@ -3387,6 +3408,47 @@
         <v>15</v>
       </c>
       <c r="M33" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="1">
+        <v>288</v>
+      </c>
+      <c r="B34" t="s" s="1">
+        <v>289</v>
+      </c>
+      <c r="C34" t="b" s="1">
+        <v>0</v>
+      </c>
+      <c r="D34" t="s" s="1">
+        <v>290</v>
+      </c>
+      <c r="E34" t="s" s="1">
+        <v>291</v>
+      </c>
+      <c r="F34" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H34" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I34" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J34" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K34" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L34" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M34" t="s" s="1">
         <v>15</v>
       </c>
     </row>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="292" count="1415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="296" count="1439">
   <si>
     <t>TestCase</t>
   </si>
@@ -888,6 +888,18 @@
   </si>
   <si>
     <t>Automation Product_20261022_191858_071: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261023_115746_432</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261023_115746_432: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261023_121205_351</t>
+  </si>
+  <si>
+    <t>Automation Public Product_20261023_121205_351: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -2807,10 +2819,10 @@
         <v>15</v>
       </c>
       <c r="D19" t="s" s="1">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="E19" t="s" s="1">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="F19" t="s" s="1">
         <v>15</v>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="296" count="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="310" count="1503">
   <si>
     <t>TestCase</t>
   </si>
@@ -900,6 +900,48 @@
   </si>
   <si>
     <t>Automation Public Product_20261023_121205_351: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261023_123333_433</t>
+  </si>
+  <si>
+    <t>Automation Product_20261023_123333_433: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261023_123745_886</t>
+  </si>
+  <si>
+    <t>Automation Product_20261023_123745_886: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Product_20261023_123745_886: Automation Linked Feature For Deletion_20261023_123829_023</t>
+  </si>
+  <si>
+    <t>Automation Linked Feature For Deletion_20261023_123829_023: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>MaturityAssessmentCompletedAssessmentValidation</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261023_124428_879</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261023_124428_879: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>SaveMaturityAssessmentWithoutSubmittingAndVerifyResume</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261023_140053_384</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261023_140053_384: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>MaturityAssesmentAtOrganisationValidateInitiateOption</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261023_152034_621</t>
   </si>
 </sst>
 </file>
@@ -2056,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -2204,10 +2246,10 @@
         <v>15</v>
       </c>
       <c r="D4" t="s" s="1">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E4" t="s" s="1">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F4" t="s" s="1">
         <v>15</v>
@@ -2245,16 +2287,16 @@
         <v>15</v>
       </c>
       <c r="D5" t="s" s="1">
-        <v>120</v>
+        <v>298</v>
       </c>
       <c r="E5" t="s" s="1">
-        <v>121</v>
+        <v>299</v>
       </c>
       <c r="F5" t="s" s="1">
-        <v>122</v>
+        <v>300</v>
       </c>
       <c r="G5" t="s" s="1">
-        <v>123</v>
+        <v>301</v>
       </c>
       <c r="H5" t="s" s="1">
         <v>15</v>
@@ -3461,6 +3503,88 @@
         <v>15</v>
       </c>
       <c r="M34" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1">
+        <v>302</v>
+      </c>
+      <c r="B35" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C35" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s" s="1">
+        <v>303</v>
+      </c>
+      <c r="E35" t="s" s="1">
+        <v>304</v>
+      </c>
+      <c r="F35" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H35" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I35" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J35" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K35" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L35" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M35" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="1">
+        <v>305</v>
+      </c>
+      <c r="B36" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s" s="1">
+        <v>306</v>
+      </c>
+      <c r="E36" t="s" s="1">
+        <v>307</v>
+      </c>
+      <c r="F36" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H36" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I36" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J36" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K36" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L36" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M36" t="s" s="1">
         <v>15</v>
       </c>
     </row>
@@ -3475,7 +3599,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -3518,6 +3642,14 @@
         <v>224</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>308</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>309</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="310" count="1503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="331" count="1614">
   <si>
     <t>TestCase</t>
   </si>
@@ -942,6 +942,69 @@
   </si>
   <si>
     <t>Org Maturity_20261023_152034_621</t>
+  </si>
+  <si>
+    <t>VerifyBaselinedAssessmentsSearchByProductNameAtProdcutLevel</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_104630_503</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_104630_503: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>VerifyCurrentAssessmentsSearchByProductNameAtProdcutLevel</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_111157_171</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_111157_171: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_123321_665</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_123321_665: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_124142_037</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_124142_037: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_125210_988</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_125210_988: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_130655_236</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_130655_236: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_131216_927</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_131216_927: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_131622_454</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261027_131622_454: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>VerifyCurrentAssessmentsSearchByTeamNameAtTeamLevel</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261027_210639_946</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261027_210639_946: Define, Design, Develop, Deploy</t>
   </si>
 </sst>
 </file>
@@ -2098,7 +2161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -3585,6 +3648,129 @@
         <v>15</v>
       </c>
       <c r="M36" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="1">
+        <v>310</v>
+      </c>
+      <c r="B37" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C37" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s" s="1">
+        <v>320</v>
+      </c>
+      <c r="E37" t="s" s="1">
+        <v>321</v>
+      </c>
+      <c r="F37" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H37" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I37" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K37" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L37" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M37" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1">
+        <v>313</v>
+      </c>
+      <c r="B38" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s" s="1">
+        <v>326</v>
+      </c>
+      <c r="E38" t="s" s="1">
+        <v>327</v>
+      </c>
+      <c r="F38" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I38" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J38" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K38" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L38" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M38" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="1">
+        <v>328</v>
+      </c>
+      <c r="B39" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s" s="1">
+        <v>329</v>
+      </c>
+      <c r="E39" t="s" s="1">
+        <v>330</v>
+      </c>
+      <c r="F39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M39" t="s" s="1">
         <v>15</v>
       </c>
     </row>

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="331" count="1614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="358" count="1761">
   <si>
     <t>TestCase</t>
   </si>
@@ -1005,6 +1005,87 @@
   </si>
   <si>
     <t>Automation Private Product Team Maturity Assessment_20261027_210639_946: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261028_084857_725, Automation Private Dependency Product_20261028_084937_520</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261028_084857_725: Define, Design, Develop, Deploy, Automation Private Dependency Product_20261028_084937_520: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261028_085334_165, Automation Private Dependency Product_20261028_085431_572</t>
+  </si>
+  <si>
+    <t>Automation Private Dependency Product_20261028_085334_165: Define, Design, Develop, Deploy, Automation Private Dependency Product_20261028_085431_572: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>MaturityAssessmentCompletedTeamLevelWithSprintAssessmentValidation</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261028_102641_336</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261028_102641_336: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261028_104536_468</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261028_104536_468: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261028_105012_272</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261028_105012_272: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261028_105611_941</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Sprint Maturity Assessment_20261028_105611_941: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261028_112029_121</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261028_112029_121: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261028_113112_175</t>
+  </si>
+  <si>
+    <t>Automation Private Product Maturity Assessment_20261028_113112_175: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261028_113319_132</t>
+  </si>
+  <si>
+    <t>Automation Private Product Team Maturity Assessment_20261028_113319_132: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261028_120936_437, Middle East Customer Service Product Dependency_20261028_121119_934</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261028_120936_437: Define, Design, Develop, Deploy, Middle East Customer Service Product Dependency_20261028_121119_934: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261028_121559_527, Middle East Customer Service Product Dependency_20261028_121732_904</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261028_121559_527: Define, Design, Develop, Deploy, Middle East Customer Service Product Dependency_20261028_121732_904: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261028_122231_845, Middle East Customer Service Product Dependency_20261028_122359_820</t>
+  </si>
+  <si>
+    <t>Middle East Customer Service Product_20261028_122231_845: Define, Design, Develop, Deploy, Middle East Customer Service Product Dependency_20261028_122359_820: Define, Design, Develop, Deploy</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261028_130054_388</t>
+  </si>
+  <si>
+    <t>Org Maturity_20261028_130318_404</t>
   </si>
 </sst>
 </file>
@@ -2161,7 +2242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -2965,10 +3046,10 @@
         <v>15</v>
       </c>
       <c r="D20" t="s" s="1">
-        <v>192</v>
+        <v>333</v>
       </c>
       <c r="E20" t="s" s="1">
-        <v>193</v>
+        <v>334</v>
       </c>
       <c r="F20" t="s" s="1">
         <v>15</v>
@@ -3164,16 +3245,16 @@
         <v>161</v>
       </c>
       <c r="B25" t="s" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D25" t="s" s="1">
-        <v>166</v>
+        <v>354</v>
       </c>
       <c r="E25" t="s" s="1">
-        <v>167</v>
+        <v>355</v>
       </c>
       <c r="F25" t="s" s="1">
         <v>15</v>
@@ -3656,16 +3737,16 @@
         <v>310</v>
       </c>
       <c r="B37" t="s" s="1">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s" s="1">
         <v>15</v>
       </c>
       <c r="D37" t="s" s="1">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="E37" t="s" s="1">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="F37" t="s" s="1">
         <v>15</v>
@@ -3703,10 +3784,10 @@
         <v>15</v>
       </c>
       <c r="D38" t="s" s="1">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="E38" t="s" s="1">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="F38" t="s" s="1">
         <v>15</v>
@@ -3738,39 +3819,80 @@
         <v>328</v>
       </c>
       <c r="B39" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s" s="1">
+        <v>348</v>
+      </c>
+      <c r="E39" t="s" s="1">
+        <v>349</v>
+      </c>
+      <c r="F39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M39" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1">
+        <v>335</v>
+      </c>
+      <c r="B40" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="C39" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="D39" t="s" s="1">
-        <v>329</v>
-      </c>
-      <c r="E39" t="s" s="1">
-        <v>330</v>
-      </c>
-      <c r="F39" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="G39" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="H39" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="I39" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="J39" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="K39" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="L39" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="M39" t="s" s="1">
+      <c r="C40" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s" s="1">
+        <v>342</v>
+      </c>
+      <c r="E40" t="s" s="1">
+        <v>343</v>
+      </c>
+      <c r="F40" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="H40" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I40" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J40" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K40" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L40" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M40" t="s" s="1">
         <v>15</v>
       </c>
     </row>
@@ -3809,7 +3931,7 @@
         <v>215</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>227</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4">

--- a/src/test/resources/output/pro/ProExecutionData.xlsx
+++ b/src/test/resources/output/pro/ProExecutionData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="358" count="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="483" count="2050">
   <si>
     <t>TestCase</t>
   </si>
@@ -1086,6 +1086,381 @@
   </si>
   <si>
     <t>Org Maturity_20261028_130318_404</t>
+  </si>
+  <si>
+    <t>createDesignProductWithMandatoryFields</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261028_200649_362</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261028_200649_362: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261028_200649_362: Customer Support Intake_20261028_200852_896</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261028_200852_896: Design</t>
+  </si>
+  <si>
+    <t>Low Level Design</t>
+  </si>
+  <si>
+    <t>Figma</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261028_200852_896: Customer Service Journey Wireframe_20261028_202709_142</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261028_202951_279</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261028_202951_279: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261028_202951_279: Customer Support Intake_20261028_203016_882</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261028_203016_882: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261028_203016_882: Customer Service Journey Wireframe_20261028_203020_881</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261028_203442_983</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261028_203442_983: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261028_203442_983: Customer Support Intake_20261028_203529_271</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261028_203529_271: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261028_203529_271: Customer Service Journey Wireframe_20261028_203538_151</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_105850_038</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_105850_038: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_105850_038: Customer Support Intake_20261029_105928_761</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_105928_761: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_105928_761: Customer Service Journey Wireframe_20261029_105933_370</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_110127_342</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_110127_342: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_110127_342: Customer Support Intake_20261029_110215_496</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_110215_496: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_110215_496: Customer Service Journey Wireframe_20261029_110220_348</t>
+  </si>
+  <si>
+    <t>createDesignWithAllFields</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_133505_562</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_133505_562: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_133505_562: Customer Support Intake_20261029_133538_564</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_133538_564: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_133538_564: Customer Support API and Routing Design_20261029_133542_581</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_134305_236</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_134305_236: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_134305_236: Customer Support Intake_20261029_134352_232</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_134352_232: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_134352_232: Customer Support API and Routing Design_20261029_134356_297</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_134724_783</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_134724_783: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_134724_783: Customer Support Intake_20261029_134756_956</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_134756_956: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_134756_956: Customer Support API and Routing Design_20261029_134801_167</t>
+  </si>
+  <si>
+    <t>addBusinessRequirementToDesign</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_171130_282</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_171130_282: Define, Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_171130_282: Customer Support Intake_20261029_171217_770</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_171217_770: Define, Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_171217_770: Accountable Support Request Ownership_20261029_171222_000</t>
+  </si>
+  <si>
+    <t>Deployment Architecture</t>
+  </si>
+  <si>
+    <t>Sketch</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_171217_770: Support Service Deployment Architecture_20261029_171226_374</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_180712_127</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_180712_127: Define, Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_180712_127: Customer Support Intake_20261029_180753_420</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_180753_420: Define, Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_180753_420: Accountable Support Request Ownership_20261029_180757_783</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_180753_420: Support Service Deployment Architecture_20261029_180805_714</t>
+  </si>
+  <si>
+    <t>createMultipleDesignsWithinFeature_lowLevelInvision</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_201042_517</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_201042_517: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261029_201042_517: Customer Support Intake_20261029_201119_917</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_201119_917: Design</t>
+  </si>
+  <si>
+    <t>Invision</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_201119_917: Support Intake Component Design_20261029_201131_424</t>
+  </si>
+  <si>
+    <t>createMultipleDesignsWithinFeature_deploymentOthers</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_201119_917: Support Platform Deployment Topology_20261029_201149_763</t>
+  </si>
+  <si>
+    <t>createMultipleDesignsWithinFeature_functionalMiro</t>
+  </si>
+  <si>
+    <t>Functional Approach</t>
+  </si>
+  <si>
+    <t>Miro</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261029_201119_917: Support Request Resolution Journey_20261029_201159_522</t>
+  </si>
+  <si>
+    <t>editDesignWithAllFields</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_105907_931</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_105907_931: Define, Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_105907_931: Customer Support Intake_20261030_105941_365</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_105941_365: Define, Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_105941_365: Accountable Support Request Ownership_20261030_105945_722, Escalation and Resolution Ownership_20261030_110006_047</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_105941_365: Support Resolution Component Blueprint_20261030_110018_378</t>
+  </si>
+  <si>
+    <t>validateDesignMandatoryFields</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_112212_108</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_112212_108: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_112212_108: Customer Support Intake_20261030_112244_686</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_112244_686: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_113033_438</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_113033_438: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_113033_438: Customer Support Intake_20261030_113103_387</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_113103_387: Design</t>
+  </si>
+  <si>
+    <t>deleteDesign</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_120119_172</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_120119_172: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_120119_172: Customer Support Intake_20261030_120158_528</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_120158_528: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_120158_528: Support Intake Design for Deletion_20261030_120205_809</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_120618_062</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_120618_062: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_120618_062: Customer Support Intake_20261030_120657_373</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_120657_373: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_120657_373: Support Intake Design for Deletion_20261030_120702_385</t>
+  </si>
+  <si>
+    <t>validateDesignLinksNavigation</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_122611_143</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_122611_143: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_122611_143: Customer Support Intake_20261030_122649_325</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_122649_325: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_122649_325: Support API Documentation Navigation_20261030_122653_972</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_124150_793</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_124150_793: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_124150_793: Customer Support Intake_20261030_124226_043</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_124226_043: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_124226_043: Customer Support API and Routing Design_20261030_124231_948</t>
+  </si>
+  <si>
+    <t>validateDocumentDownloadedAndValidation</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_124455_353</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_124455_353: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_124455_353: Customer Support Intake_20261030_124530_191</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_124530_191: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_124530_191: Customer Support Workflow Specification_20261030_124534_918</t>
+  </si>
+  <si>
+    <t>searchDesign_first</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_140446_049</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_140446_049: Design</t>
+  </si>
+  <si>
+    <t>Customer Experience Design Product_20261030_140446_049: Customer Support Intake_20261030_140524_379</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_140524_379: Design</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_140524_379: Customer Support Intake Screen_20261030_140535_181</t>
+  </si>
+  <si>
+    <t>searchDesign_second</t>
+  </si>
+  <si>
+    <t>Customer Support Intake_20261030_140524_379: Ticket Resolution Workflow_20261030_140539_122</t>
   </si>
 </sst>
 </file>
@@ -2242,7 +2617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="27.1719"/>
@@ -3893,6 +4268,539 @@
         <v>15</v>
       </c>
       <c r="M40" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="1">
+        <v>358</v>
+      </c>
+      <c r="B41" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s" s="1">
+        <v>381</v>
+      </c>
+      <c r="E41" t="s" s="1">
+        <v>382</v>
+      </c>
+      <c r="F41" t="s" s="1">
+        <v>383</v>
+      </c>
+      <c r="G41" t="s" s="1">
+        <v>384</v>
+      </c>
+      <c r="H41" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I41" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="J41" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="K41" t="s" s="1">
+        <v>385</v>
+      </c>
+      <c r="L41" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M41" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="1">
+        <v>386</v>
+      </c>
+      <c r="B42" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s" s="1">
+        <v>464</v>
+      </c>
+      <c r="E42" t="s" s="1">
+        <v>465</v>
+      </c>
+      <c r="F42" t="s" s="1">
+        <v>466</v>
+      </c>
+      <c r="G42" t="s" s="1">
+        <v>467</v>
+      </c>
+      <c r="H42" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="J42" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="K42" t="s" s="1">
+        <v>468</v>
+      </c>
+      <c r="L42" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M42" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="1">
+        <v>402</v>
+      </c>
+      <c r="B43" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C43" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s" s="1">
+        <v>411</v>
+      </c>
+      <c r="E43" t="s" s="1">
+        <v>412</v>
+      </c>
+      <c r="F43" t="s" s="1">
+        <v>413</v>
+      </c>
+      <c r="G43" t="s" s="1">
+        <v>414</v>
+      </c>
+      <c r="H43" t="s" s="1">
+        <v>415</v>
+      </c>
+      <c r="I43" t="s" s="1">
+        <v>408</v>
+      </c>
+      <c r="J43" t="s" s="1">
+        <v>409</v>
+      </c>
+      <c r="K43" t="s" s="1">
+        <v>416</v>
+      </c>
+      <c r="L43" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M43" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="1">
+        <v>417</v>
+      </c>
+      <c r="B44" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s" s="1">
+        <v>418</v>
+      </c>
+      <c r="E44" t="s" s="1">
+        <v>419</v>
+      </c>
+      <c r="F44" t="s" s="1">
+        <v>420</v>
+      </c>
+      <c r="G44" t="s" s="1">
+        <v>421</v>
+      </c>
+      <c r="H44" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I44" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="J44" t="s" s="1">
+        <v>422</v>
+      </c>
+      <c r="K44" t="s" s="1">
+        <v>423</v>
+      </c>
+      <c r="L44" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M44" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="1">
+        <v>424</v>
+      </c>
+      <c r="B45" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s" s="1">
+        <v>418</v>
+      </c>
+      <c r="E45" t="s" s="1">
+        <v>419</v>
+      </c>
+      <c r="F45" t="s" s="1">
+        <v>420</v>
+      </c>
+      <c r="G45" t="s" s="1">
+        <v>421</v>
+      </c>
+      <c r="H45" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I45" t="s" s="1">
+        <v>408</v>
+      </c>
+      <c r="J45" t="s" s="1">
+        <v>425</v>
+      </c>
+      <c r="K45" t="s" s="1">
+        <v>426</v>
+      </c>
+      <c r="L45" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M45" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1">
+        <v>427</v>
+      </c>
+      <c r="B46" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C46" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s" s="1">
+        <v>418</v>
+      </c>
+      <c r="E46" t="s" s="1">
+        <v>419</v>
+      </c>
+      <c r="F46" t="s" s="1">
+        <v>420</v>
+      </c>
+      <c r="G46" t="s" s="1">
+        <v>421</v>
+      </c>
+      <c r="H46" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I46" t="s" s="1">
+        <v>428</v>
+      </c>
+      <c r="J46" t="s" s="1">
+        <v>429</v>
+      </c>
+      <c r="K46" t="s" s="1">
+        <v>430</v>
+      </c>
+      <c r="L46" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M46" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="1">
+        <v>431</v>
+      </c>
+      <c r="B47" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C47" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s" s="1">
+        <v>432</v>
+      </c>
+      <c r="E47" t="s" s="1">
+        <v>433</v>
+      </c>
+      <c r="F47" t="s" s="1">
+        <v>434</v>
+      </c>
+      <c r="G47" t="s" s="1">
+        <v>435</v>
+      </c>
+      <c r="H47" t="s" s="1">
+        <v>436</v>
+      </c>
+      <c r="I47" t="s" s="1">
+        <v>408</v>
+      </c>
+      <c r="J47" t="s" s="1">
+        <v>409</v>
+      </c>
+      <c r="K47" t="s" s="1">
+        <v>437</v>
+      </c>
+      <c r="L47" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M47" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
+        <v>438</v>
+      </c>
+      <c r="B48" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="C48" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s" s="1">
+        <v>443</v>
+      </c>
+      <c r="E48" t="s" s="1">
+        <v>444</v>
+      </c>
+      <c r="F48" t="s" s="1">
+        <v>445</v>
+      </c>
+      <c r="G48" t="s" s="1">
+        <v>446</v>
+      </c>
+      <c r="H48" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I48" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="J48" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="K48" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="L48" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M48" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="1">
+        <v>447</v>
+      </c>
+      <c r="B49" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s" s="1">
+        <v>453</v>
+      </c>
+      <c r="E49" t="s" s="1">
+        <v>454</v>
+      </c>
+      <c r="F49" t="s" s="1">
+        <v>455</v>
+      </c>
+      <c r="G49" t="s" s="1">
+        <v>456</v>
+      </c>
+      <c r="H49" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I49" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="J49" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="K49" t="s" s="1">
+        <v>457</v>
+      </c>
+      <c r="L49" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M49" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1">
+        <v>458</v>
+      </c>
+      <c r="B50" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C50" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s" s="1">
+        <v>459</v>
+      </c>
+      <c r="E50" t="s" s="1">
+        <v>460</v>
+      </c>
+      <c r="F50" t="s" s="1">
+        <v>461</v>
+      </c>
+      <c r="G50" t="s" s="1">
+        <v>462</v>
+      </c>
+      <c r="H50" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I50" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="J50" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="K50" t="s" s="1">
+        <v>463</v>
+      </c>
+      <c r="L50" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M50" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="1">
+        <v>469</v>
+      </c>
+      <c r="B51" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C51" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s" s="1">
+        <v>470</v>
+      </c>
+      <c r="E51" t="s" s="1">
+        <v>471</v>
+      </c>
+      <c r="F51" t="s" s="1">
+        <v>472</v>
+      </c>
+      <c r="G51" t="s" s="1">
+        <v>473</v>
+      </c>
+      <c r="H51" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I51" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="J51" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="K51" t="s" s="1">
+        <v>474</v>
+      </c>
+      <c r="L51" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M51" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="1">
+        <v>475</v>
+      </c>
+      <c r="B52" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C52" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s" s="1">
+        <v>476</v>
+      </c>
+      <c r="E52" t="s" s="1">
+        <v>477</v>
+      </c>
+      <c r="F52" t="s" s="1">
+        <v>478</v>
+      </c>
+      <c r="G52" t="s" s="1">
+        <v>479</v>
+      </c>
+      <c r="H52" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I52" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="J52" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="K52" t="s" s="1">
+        <v>480</v>
+      </c>
+      <c r="L52" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M52" t="s" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="1">
+        <v>481</v>
+      </c>
+      <c r="B53" t="s" s="1">
+        <v>14</v>
+      </c>
+      <c r="C53" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="D53" t="s" s="1">
+        <v>476</v>
+      </c>
+      <c r="E53" t="s" s="1">
+        <v>477</v>
+      </c>
+      <c r="F53" t="s" s="1">
+        <v>478</v>
+      </c>
+      <c r="G53" t="s" s="1">
+        <v>479</v>
+      </c>
+      <c r="H53" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="I53" t="s" s="1">
+        <v>363</v>
+      </c>
+      <c r="J53" t="s" s="1">
+        <v>364</v>
+      </c>
+      <c r="K53" t="s" s="1">
+        <v>482</v>
+      </c>
+      <c r="L53" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="M53" t="s" s="1">
         <v>15</v>
       </c>
     </row>
